--- a/output/pdf_financials_xlsx/LITS.xlsx
+++ b/output/pdf_financials_xlsx/LITS.xlsx
@@ -2211,16 +2211,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.0276</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.154838</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.578335</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.814672</v>
       </c>
     </row>
     <row r="93">
@@ -3826,7 +3826,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -4230,7 +4234,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -4600,7 +4608,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
         <v>0.0276</v>
       </c>

--- a/output/pdf_financials_xlsx/LITS.xlsx
+++ b/output/pdf_financials_xlsx/LITS.xlsx
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.352085</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.577669</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.691178</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.021197</v>
       </c>
     </row>
     <row r="35">
@@ -1115,16 +1115,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.352085</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.577669</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.691178</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.021197</v>
       </c>
     </row>
     <row r="37">
@@ -1343,16 +1343,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.352085</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.883727</v>
+        <v>0.306058</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.927967</v>
+        <v>0.236789</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.036948</v>
+        <v>0.015751</v>
       </c>
     </row>
     <row r="49">
@@ -2813,10 +2813,10 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.019584</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.021091</v>
       </c>
     </row>
     <row r="125">
@@ -2832,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.019584</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.021091</v>
       </c>
     </row>
     <row r="126">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5456,7 +5456,11 @@
           <t>Lease payments 12</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/LITS.xlsx
+++ b/output/pdf_financials_xlsx/LITS.xlsx
@@ -2376,10 +2376,10 @@
         <v>0.037057</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.047881</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.064722</v>
       </c>
     </row>
     <row r="102">
@@ -2471,10 +2471,10 @@
         <v>-0.010206</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.51068</v>
+        <v>0.462799</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>1.431343</v>
+        <v>1.496065</v>
       </c>
     </row>
     <row r="107">
@@ -5104,7 +5104,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
